--- a/Docs/Flow/Users.xlsx
+++ b/Docs/Flow/Users.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Live\Coolzo\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Live\Coolzo\Backend\Docs\Flow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489370C4-2A29-4056-BFB5-EA6EBE114DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74D2969-9588-4D5A-814C-1B02C874FBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{B6122899-EBA7-424A-8406-D2C03CDB995D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{B6122899-EBA7-424A-8406-D2C03CDB995D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="issues" sheetId="2" r:id="rId2"/>
+    <sheet name="Roles" sheetId="1" r:id="rId1"/>
+    <sheet name="Issues" sheetId="2" r:id="rId2"/>
+    <sheet name="Modules" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="137">
   <si>
     <t>Email</t>
   </si>
@@ -396,12 +397,198 @@
 in the page the download opeiton is not working. 
 class="lucide lucide-download"</t>
   </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Key Areas</t>
+  </si>
+  <si>
+    <t>Project Identity</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>Brand, RBAC, design</t>
+  </si>
+  <si>
+    <t>Service Request Management</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>SR lifecycle, dispatch, timeline</t>
+  </si>
+  <si>
+    <t>Field Workflow</t>
+  </si>
+  <si>
+    <t>Tech mobile, checkins, job reports</t>
+  </si>
+  <si>
+    <t>Customer Master (360)</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>Customers, addresses, notes</t>
+  </si>
+  <si>
+    <t>Equipment Register</t>
+  </si>
+  <si>
+    <t>Serial, warranty, service history</t>
+  </si>
+  <si>
+    <t>AMC Contract Engine</t>
+  </si>
+  <si>
+    <t>Plans, visits, renewals</t>
+  </si>
+  <si>
+    <t>Warranty Management</t>
+  </si>
+  <si>
+    <t>Records, eligibility</t>
+  </si>
+  <si>
+    <t>Booking Engine</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>Slots, wizard, OTP, coupons</t>
+  </si>
+  <si>
+    <t>Billing &amp; Payments</t>
+  </si>
+  <si>
+    <t>S5</t>
+  </si>
+  <si>
+    <t>Invoices, AR, tax</t>
+  </si>
+  <si>
+    <t>Estimates &amp; Work Orders</t>
+  </si>
+  <si>
+    <t>S6</t>
+  </si>
+  <si>
+    <t>Estimates, approvals, WOs</t>
+  </si>
+  <si>
+    <t>Inventory &amp; Parts</t>
+  </si>
+  <si>
+    <t>Stock, POs, parts requests</t>
+  </si>
+  <si>
+    <t>Customer Portal (Web)</t>
+  </si>
+  <si>
+    <t>S7</t>
+  </si>
+  <si>
+    <t>Dashboard, bookings, tracker</t>
+  </si>
+  <si>
+    <t>Customer Portal (Mobile)</t>
+  </si>
+  <si>
+    <t>Quick book, offline, push</t>
+  </si>
+  <si>
+    <t>Admin Operations</t>
+  </si>
+  <si>
+    <t>Dispatch, SLA, map, board</t>
+  </si>
+  <si>
+    <t>Dispatch Management</t>
+  </si>
+  <si>
+    <t>Assign, reassign, batch</t>
+  </si>
+  <si>
+    <t>Technician Management</t>
+  </si>
+  <si>
+    <t>S8</t>
+  </si>
+  <si>
+    <t>Skills, zones, attendance, GPS</t>
+  </si>
+  <si>
+    <t>Scheduling Board</t>
+  </si>
+  <si>
+    <t>Calendar, conflicts, shifts</t>
+  </si>
+  <si>
+    <t>Master Data &amp; Config</t>
+  </si>
+  <si>
+    <t>S9</t>
+  </si>
+  <si>
+    <t>Zones, pricing, SLA, CMS</t>
+  </si>
+  <si>
+    <t>Notifications &amp; Comms</t>
+  </si>
+  <si>
+    <t>Templates, WhatsApp, push, logs</t>
+  </si>
+  <si>
+    <t>CMS &amp; Content</t>
+  </si>
+  <si>
+    <t>Banners, blog, FAQs</t>
+  </si>
+  <si>
+    <t>Reports &amp; Audit</t>
+  </si>
+  <si>
+    <t>Dashboards, exports, compliance</t>
+  </si>
+  <si>
+    <t>Authentication &amp; Security</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>JWT, OTP, 2FA, RBAC</t>
+  </si>
+  <si>
+    <t>API Architecture</t>
+  </si>
+  <si>
+    <t>Versioning, pagination, rate-limit</t>
+  </si>
+  <si>
+    <t>Database Architecture</t>
+  </si>
+  <si>
+    <t>EF Core, migrations, soft-delete</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,6 +633,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -489,7 +684,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -518,6 +713,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1313,4 +1510,371 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674225BC-D9CD-433E-8EEF-6BB1AE9FA861}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="11">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="11">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="11">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="11">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="11">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>